--- a/قوالب_أصناف_المحلات_Excel/09_صيدليات_ومستحضرات_تجميل_وعناية.xlsx
+++ b/قوالب_أصناف_المحلات_Excel/09_صيدليات_ومستحضرات_تجميل_وعناية.xlsx
@@ -397,1269 +397,1933 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:N45"/>
   <cols>
-    <col min="1" max="1" width="44.83203125" customWidth="1"/>
+    <col min="1" max="1" width="42.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>اسم الصنف</v>
-      </c>
-      <c r="B1" t="str">
-        <v>الباركود الرئيسي</v>
-      </c>
-      <c r="C1" t="str">
-        <v>القسم / التصنيف</v>
-      </c>
-      <c r="D1" t="str">
-        <v>الوحدة</v>
-      </c>
-      <c r="E1" t="str">
-        <v>سعر البيع</v>
-      </c>
-      <c r="F1" t="str">
-        <v>سعر التكلفة</v>
-      </c>
-      <c r="G1" t="str">
-        <v>الرصيد الافتتاحي</v>
-      </c>
-      <c r="H1" t="str">
-        <v>حد الطلب الأدنى</v>
-      </c>
-      <c r="I1" t="str">
-        <v>كود الصنف الداخلي</v>
+        <v>رفيق POS - نموذج استيراد الأصناف المعتمد للمتاجر</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>بنادول إكسترا أحمر شريط 12 قرص</v>
-      </c>
-      <c r="B2" t="str">
-        <v>6221100010015</v>
-      </c>
-      <c r="C2" t="str">
-        <v>أدوية ومسكنات شائعة</v>
-      </c>
-      <c r="D2" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E2">
-        <v>42</v>
-      </c>
-      <c r="F2">
-        <v>34</v>
-      </c>
-      <c r="G2">
-        <v>50</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2" t="str">
-        <v>SKU-0001</v>
+        <v>تعليمات هامة: الأعمدة المميزة بنجمة (*) إلزامية | الباركودات تحفظ كنص | اللون والمقاس اختياريان لمحلات الملابس والأحذية | الوحدة: قطعة أو كجم | المبالغ بالجنيه المصري</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>بنادول أزرق خافض حرارة شريط 12 قرص</v>
+        <v>اسم الصنف *</v>
       </c>
       <c r="B3" t="str">
-        <v>6221100010022</v>
+        <v>الباركود الرئيسي</v>
       </c>
       <c r="C3" t="str">
-        <v>أدوية ومسكنات شائعة</v>
+        <v>باركودات إضافية (مفصولة بفاصلة)</v>
       </c>
       <c r="D3" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E3">
-        <v>35</v>
-      </c>
-      <c r="F3">
-        <v>28.5</v>
-      </c>
-      <c r="G3">
-        <v>50</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
+        <v>القسم / التصنيف</v>
+      </c>
+      <c r="E3" t="str">
+        <v>الوحدة (قطعة / كجم)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>اللون (اختياري / للملابس)</v>
+      </c>
+      <c r="G3" t="str">
+        <v>المقاس (اختياري / للملابس)</v>
+      </c>
+      <c r="H3" t="str">
+        <v>سعر البيع (بالجنيه) *</v>
       </c>
       <c r="I3" t="str">
-        <v>SKU-0002</v>
+        <v>سعر التكلفة (بالجنيه)</v>
+      </c>
+      <c r="J3" t="str">
+        <v>الرصيد الافتتاحي</v>
+      </c>
+      <c r="K3" t="str">
+        <v>حد الطلب الأدنى</v>
+      </c>
+      <c r="L3" t="str">
+        <v>نسبة الضريبة (%)</v>
+      </c>
+      <c r="M3" t="str">
+        <v>كود الصنف الداخلي (SKU)</v>
+      </c>
+      <c r="N3" t="str">
+        <v>كود التصنيف الضريبي (GS1/EGS)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>كونجستال نزلات برد وإنفلونزا شريط 10 أقراص</v>
+        <v>بنادول إكسترا أحمر شريط 12 قرص</v>
       </c>
       <c r="B4" t="str">
-        <v>6221100010039</v>
+        <v>6221100010015</v>
       </c>
       <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D4" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E4">
-        <v>28</v>
-      </c>
-      <c r="F4">
-        <v>22</v>
-      </c>
-      <c r="G4">
-        <v>60</v>
+      <c r="E4" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
       </c>
       <c r="H4">
-        <v>12</v>
-      </c>
-      <c r="I4" t="str">
-        <v>SKU-0003</v>
+        <v>42</v>
+      </c>
+      <c r="I4">
+        <v>34</v>
+      </c>
+      <c r="J4">
+        <v>50</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="str">
+        <v>PHR-0001</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>سيتال خافض حرارة للأطفال شراب 120 مل</v>
+        <v>بنادول أزرق خافض حرارة شريط 12 قرص</v>
       </c>
       <c r="B5" t="str">
-        <v>6221100010046</v>
+        <v>6221100010022</v>
       </c>
       <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D5" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>14.5</v>
-      </c>
-      <c r="G5">
-        <v>40</v>
+      <c r="E5" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
       </c>
       <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5" t="str">
-        <v>SKU-0004</v>
+        <v>35</v>
+      </c>
+      <c r="I5">
+        <v>28.5</v>
+      </c>
+      <c r="J5">
+        <v>50</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="str">
+        <v>PHR-0002</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>بروفين مسكن ومضاد للالتهاب 400 مجم شريط 10 أقراص</v>
+        <v>كونجستال نزلات برد وإنفلونزا شريط 10 أقراص</v>
       </c>
       <c r="B6" t="str">
-        <v>6221100010053</v>
+        <v>6221100010039</v>
       </c>
       <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D6" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E6">
-        <v>26</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
+      <c r="E6" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
       </c>
       <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6" t="str">
-        <v>SKU-0005</v>
+        <v>28</v>
+      </c>
+      <c r="I6">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>60</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="str">
+        <v>PHR-0003</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>أنتينال كبسول مطهر معوي شريط 12 كبسولة</v>
+        <v>سيتال خافض حرارة للأطفال شراب 120 مل</v>
       </c>
       <c r="B7" t="str">
-        <v>6221100010060</v>
+        <v>6221100010046</v>
       </c>
       <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D7" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E7">
-        <v>32</v>
-      </c>
-      <c r="F7">
-        <v>26</v>
-      </c>
-      <c r="G7">
-        <v>60</v>
+      <c r="E7" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7">
-        <v>15</v>
-      </c>
-      <c r="I7" t="str">
-        <v>SKU-0006</v>
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>14.5</v>
+      </c>
+      <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="str">
+        <v>PHR-0004</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ستربسلز استحلاب لالتهاب الحلق عسل وليمون باكت</v>
+        <v>بروفين مسكن ومضاد للالتهاب 400 مجم شريط 10 أقراص</v>
       </c>
       <c r="B8" t="str">
-        <v>6221100010077</v>
+        <v>6221100010053</v>
       </c>
       <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D8" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E8">
-        <v>95</v>
-      </c>
-      <c r="F8">
-        <v>78</v>
-      </c>
-      <c r="G8">
-        <v>30</v>
+      <c r="E8" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
       </c>
       <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8" t="str">
-        <v>SKU-0007</v>
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>50</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="str">
+        <v>PHR-0005</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>أوتريفين بخاخ أنف للبالغين 10 مل</v>
+        <v>أنتينال كبسول مطهر معوي شريط 12 كبسولة</v>
       </c>
       <c r="B9" t="str">
-        <v>6221100010084</v>
+        <v>6221100010060</v>
       </c>
       <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D9" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E9">
-        <v>24</v>
-      </c>
-      <c r="F9">
-        <v>19</v>
-      </c>
-      <c r="G9">
-        <v>40</v>
+      <c r="E9" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
       </c>
       <c r="H9">
-        <v>8</v>
-      </c>
-      <c r="I9" t="str">
-        <v>SKU-0008</v>
+        <v>32</v>
+      </c>
+      <c r="I9">
+        <v>26</v>
+      </c>
+      <c r="J9">
+        <v>60</v>
+      </c>
+      <c r="K9">
+        <v>15</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="str">
+        <v>PHR-0006</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>فوار راني لعلاج الحموضة باكت 6 أكياس</v>
+        <v>ستربسلز استحلاب لالتهاب الحلق عسل وليمون باكت</v>
       </c>
       <c r="B10" t="str">
-        <v>6221100010091</v>
+        <v>6221100010077</v>
       </c>
       <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D10" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
-      </c>
-      <c r="F10">
-        <v>16</v>
-      </c>
-      <c r="G10">
-        <v>50</v>
+      <c r="E10" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
       </c>
       <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10" t="str">
-        <v>SKU-0009</v>
+        <v>95</v>
+      </c>
+      <c r="I10">
+        <v>78</v>
+      </c>
+      <c r="J10">
+        <v>30</v>
+      </c>
+      <c r="K10">
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="str">
+        <v>PHR-0007</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>فوار كول يورين مسالك بولية باكت 6 أكياس</v>
+        <v>أوتريفين بخاخ أنف للبالغين 10 مل</v>
       </c>
       <c r="B11" t="str">
-        <v>6221100010107</v>
+        <v>6221100010084</v>
       </c>
       <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D11" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E11">
-        <v>22</v>
-      </c>
-      <c r="F11">
-        <v>17.5</v>
-      </c>
-      <c r="G11">
+      <c r="E11" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>19</v>
+      </c>
+      <c r="J11">
         <v>40</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>8</v>
       </c>
-      <c r="I11" t="str">
-        <v>SKU-0010</v>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="str">
+        <v>PHR-0008</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ألفينترن أقراص مضاد للتورم والالتهاب شريط 10 أقراص</v>
+        <v>فوار راني لعلاج الحموضة باكت 6 أكياس</v>
       </c>
       <c r="B12" t="str">
-        <v>6221100010114</v>
+        <v>6221100010091</v>
       </c>
       <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D12" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E12">
-        <v>30</v>
-      </c>
-      <c r="F12">
-        <v>24.5</v>
-      </c>
-      <c r="G12">
+      <c r="E12" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>16</v>
+      </c>
+      <c r="J12">
         <v>50</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>10</v>
       </c>
-      <c r="I12" t="str">
-        <v>SKU-0011</v>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="str">
+        <v>PHR-0009</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>كتافلام 50 مجم مسكن سريع شريط 10 أقراص</v>
+        <v>فوار كول يورين مسالك بولية باكت 6 أكياس</v>
       </c>
       <c r="B13" t="str">
-        <v>6221100010121</v>
+        <v>6221100010107</v>
       </c>
       <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
         <v>أدوية ومسكنات شائعة</v>
       </c>
-      <c r="D13" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E13">
-        <v>38</v>
-      </c>
-      <c r="F13">
-        <v>31</v>
-      </c>
-      <c r="G13">
-        <v>50</v>
+      <c r="E13" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
       </c>
       <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="I13" t="str">
-        <v>SKU-0012</v>
+        <v>22</v>
+      </c>
+      <c r="I13">
+        <v>17.5</v>
+      </c>
+      <c r="J13">
+        <v>40</v>
+      </c>
+      <c r="K13">
+        <v>8</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="str">
+        <v>PHR-0010</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>كحول طبي معقم إيثيلي 70% بخاخ 120 مل</v>
+        <v>ألفينترن أقراص مضاد للتورم والالتهاب شريط 10 أقراص</v>
       </c>
       <c r="B14" t="str">
-        <v>6221100020014</v>
+        <v>6221100010114</v>
       </c>
       <c r="C14" t="str">
-        <v>مستلزمات وإسعافات</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E14">
-        <v>25</v>
-      </c>
-      <c r="F14">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>60</v>
+        <v>أدوية ومسكنات شائعة</v>
+      </c>
+      <c r="E14" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
       </c>
       <c r="H14">
-        <v>12</v>
-      </c>
-      <c r="I14" t="str">
-        <v>SKU-0013</v>
+        <v>30</v>
+      </c>
+      <c r="I14">
+        <v>24.5</v>
+      </c>
+      <c r="J14">
+        <v>50</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="str">
+        <v>PHR-0011</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>بيتادين مطهر جروح سائل 60 مل</v>
+        <v>كتافلام 50 مجم مسكن سريع شريط 10 أقراص</v>
       </c>
       <c r="B15" t="str">
-        <v>6221100020021</v>
+        <v>6221100010121</v>
       </c>
       <c r="C15" t="str">
-        <v>مستلزمات وإسعافات</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E15">
-        <v>45</v>
-      </c>
-      <c r="F15">
-        <v>36</v>
-      </c>
-      <c r="G15">
-        <v>40</v>
+        <v>أدوية ومسكنات شائعة</v>
+      </c>
+      <c r="E15" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
       </c>
       <c r="H15">
-        <v>8</v>
-      </c>
-      <c r="I15" t="str">
-        <v>SKU-0014</v>
+        <v>38</v>
+      </c>
+      <c r="I15">
+        <v>31</v>
+      </c>
+      <c r="J15">
+        <v>50</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="str">
+        <v>PHR-0012</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>قطن طبي ممتص فاخر معقم 100 جم</v>
+        <v>كحول طبي معقم إيثيلي 70% بخاخ 120 مل</v>
       </c>
       <c r="B16" t="str">
-        <v>6221100020038</v>
+        <v>6221100020014</v>
       </c>
       <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D16" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E16">
-        <v>22</v>
-      </c>
-      <c r="F16">
-        <v>15</v>
-      </c>
-      <c r="G16">
-        <v>50</v>
+      <c r="E16" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
       </c>
       <c r="H16">
-        <v>10</v>
-      </c>
-      <c r="I16" t="str">
-        <v>SKU-0015</v>
+        <v>25</v>
+      </c>
+      <c r="I16">
+        <v>16</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+      <c r="K16">
+        <v>12</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="str">
+        <v>PHR-0013</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>شاش طبي معقم باكت 5 قطع</v>
+        <v>بيتادين مطهر جروح سائل 60 مل</v>
       </c>
       <c r="B17" t="str">
-        <v>6221100020045</v>
+        <v>6221100020021</v>
       </c>
       <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D17" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E17">
-        <v>15</v>
-      </c>
-      <c r="F17">
-        <v>9.5</v>
-      </c>
-      <c r="G17">
-        <v>60</v>
+      <c r="E17" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
       </c>
       <c r="H17">
-        <v>15</v>
-      </c>
-      <c r="I17" t="str">
-        <v>SKU-0016</v>
+        <v>45</v>
+      </c>
+      <c r="I17">
+        <v>36</v>
+      </c>
+      <c r="J17">
+        <v>40</v>
+      </c>
+      <c r="K17">
+        <v>8</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="str">
+        <v>PHR-0014</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>بلاستر طبي لاصق جروح علبة 50 قطعة</v>
+        <v>قطن طبي ممتص فاخر معقم 100 جم</v>
       </c>
       <c r="B18" t="str">
-        <v>6221100020052</v>
+        <v>6221100020038</v>
       </c>
       <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D18" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E18">
-        <v>30</v>
-      </c>
-      <c r="F18">
-        <v>18</v>
-      </c>
-      <c r="G18">
-        <v>40</v>
+      <c r="E18" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
       </c>
       <c r="H18">
-        <v>8</v>
-      </c>
-      <c r="I18" t="str">
-        <v>SKU-0017</v>
+        <v>22</v>
+      </c>
+      <c r="I18">
+        <v>15</v>
+      </c>
+      <c r="J18">
+        <v>50</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="str">
+        <v>PHR-0015</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>رباط ضاغط طبي مرن مقاس 10 سم</v>
+        <v>شاش طبي معقم باكت 5 قطع</v>
       </c>
       <c r="B19" t="str">
-        <v>6221100020069</v>
+        <v>6221100020045</v>
       </c>
       <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D19" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E19">
-        <v>20</v>
-      </c>
-      <c r="F19">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>35</v>
+      <c r="E19" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
       </c>
       <c r="H19">
-        <v>7</v>
-      </c>
-      <c r="I19" t="str">
-        <v>SKU-0018</v>
+        <v>15</v>
+      </c>
+      <c r="I19">
+        <v>9.5</v>
+      </c>
+      <c r="J19">
+        <v>60</v>
+      </c>
+      <c r="K19">
+        <v>15</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="str">
+        <v>PHR-0016</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ترمومتر رقمي ديجيتال لقياس الحرارة شاشة LCD</v>
+        <v>بلاستر طبي لاصق جروح علبة 50 قطعة</v>
       </c>
       <c r="B20" t="str">
-        <v>6221100020076</v>
+        <v>6221100020052</v>
       </c>
       <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D20" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E20">
-        <v>75</v>
-      </c>
-      <c r="F20">
-        <v>48</v>
-      </c>
-      <c r="G20">
-        <v>20</v>
+      <c r="E20" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
       </c>
       <c r="H20">
-        <v>4</v>
-      </c>
-      <c r="I20" t="str">
-        <v>SKU-0019</v>
+        <v>30</v>
+      </c>
+      <c r="I20">
+        <v>18</v>
+      </c>
+      <c r="J20">
+        <v>40</v>
+      </c>
+      <c r="K20">
+        <v>8</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="str">
+        <v>PHR-0017</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>سرنجة طبية معقمة 3 سم سن دقيق كرتونة 100</v>
+        <v>رباط ضاغط طبي مرن مقاس 10 سم</v>
       </c>
       <c r="B21" t="str">
-        <v>6221100020083</v>
+        <v>6221100020069</v>
       </c>
       <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D21" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E21">
-        <v>2.5</v>
-      </c>
-      <c r="F21">
-        <v>1.6</v>
-      </c>
-      <c r="G21">
-        <v>200</v>
+      <c r="E21" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>10 سم</v>
       </c>
       <c r="H21">
-        <v>40</v>
-      </c>
-      <c r="I21" t="str">
-        <v>SKU-0020</v>
+        <v>20</v>
+      </c>
+      <c r="I21">
+        <v>12</v>
+      </c>
+      <c r="J21">
+        <v>35</v>
+      </c>
+      <c r="K21">
+        <v>7</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="str">
+        <v>PHR-0018</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>سرنجة طبية معقمة 5 سم كرتونة 100</v>
+        <v>ترمومتر رقمي ديجيتال لقياس الحرارة شاشة LCD</v>
       </c>
       <c r="B22" t="str">
-        <v>6221100020090</v>
+        <v>6221100020076</v>
       </c>
       <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D22" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22">
-        <v>1.9</v>
-      </c>
-      <c r="G22">
-        <v>200</v>
+      <c r="E22" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
       </c>
       <c r="H22">
-        <v>40</v>
-      </c>
-      <c r="I22" t="str">
-        <v>SKU-0021</v>
+        <v>75</v>
+      </c>
+      <c r="I22">
+        <v>48</v>
+      </c>
+      <c r="J22">
+        <v>20</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="str">
+        <v>PHR-0019</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>كمامة طبية 3 طبقات دعامة أنف باكت 50 قطعة</v>
+        <v>سرنجة طبية معقمة 3 سم سن دقيق كرتونة 100</v>
       </c>
       <c r="B23" t="str">
-        <v>6221100020106</v>
+        <v>6221100020083</v>
       </c>
       <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
         <v>مستلزمات وإسعافات</v>
       </c>
-      <c r="D23" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E23">
+      <c r="E23" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>3 سم</v>
+      </c>
+      <c r="H23">
+        <v>2.5</v>
+      </c>
+      <c r="I23">
+        <v>1.6</v>
+      </c>
+      <c r="J23">
+        <v>200</v>
+      </c>
+      <c r="K23">
         <v>40</v>
       </c>
-      <c r="F23">
-        <v>24</v>
-      </c>
-      <c r="G23">
-        <v>50</v>
-      </c>
-      <c r="H23">
-        <v>10</v>
-      </c>
-      <c r="I23" t="str">
-        <v>SKU-0022</v>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="str">
+        <v>PHR-0020</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>حفاضات بامبرز مقاس 3 عبوة التوفير 58 حفاضة</v>
+        <v>سرنجة طبية معقمة 5 سم كرتونة 100</v>
       </c>
       <c r="B24" t="str">
-        <v>6221100030013</v>
+        <v>6221100020090</v>
       </c>
       <c r="C24" t="str">
-        <v>عناية بالأم والطفل</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E24">
-        <v>290</v>
-      </c>
-      <c r="F24">
-        <v>255</v>
-      </c>
-      <c r="G24">
-        <v>25</v>
+        <v>مستلزمات وإسعافات</v>
+      </c>
+      <c r="E24" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>5 سم</v>
       </c>
       <c r="H24">
-        <v>5</v>
-      </c>
-      <c r="I24" t="str">
-        <v>SKU-0023</v>
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>1.9</v>
+      </c>
+      <c r="J24">
+        <v>200</v>
+      </c>
+      <c r="K24">
+        <v>40</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="str">
+        <v>PHR-0021</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>حفاضات بامبرز مقاس 4 عبوة جامبو 64 حفاضة</v>
+        <v>كمامة طبية 3 طبقات دعامة أنف باكت 50 قطعة</v>
       </c>
       <c r="B25" t="str">
-        <v>6221100030020</v>
+        <v>6221100020106</v>
       </c>
       <c r="C25" t="str">
-        <v>عناية بالأم والطفل</v>
+        <v/>
       </c>
       <c r="D25" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E25">
-        <v>320</v>
-      </c>
-      <c r="F25">
-        <v>280</v>
-      </c>
-      <c r="G25">
-        <v>25</v>
+        <v>مستلزمات وإسعافات</v>
+      </c>
+      <c r="E25" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F25" t="str">
+        <v>أزرق</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
       </c>
       <c r="H25">
-        <v>5</v>
-      </c>
-      <c r="I25" t="str">
-        <v>SKU-0024</v>
+        <v>40</v>
+      </c>
+      <c r="I25">
+        <v>24</v>
+      </c>
+      <c r="J25">
+        <v>50</v>
+      </c>
+      <c r="K25">
+        <v>10</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="str">
+        <v>PHR-0022</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>حفاضات مولفيكس مقاس 3 عبوة 58 حفاضة</v>
+        <v>حفاضات بامبرز مقاس 3 عبوة التوفير 58 حفاضة</v>
       </c>
       <c r="B26" t="str">
-        <v>6221100030037</v>
+        <v>6221100030013</v>
       </c>
       <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
         <v>عناية بالأم والطفل</v>
       </c>
-      <c r="D26" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E26">
-        <v>260</v>
-      </c>
-      <c r="F26">
-        <v>228</v>
-      </c>
-      <c r="G26">
+      <c r="E26" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>مقاس 3</v>
+      </c>
+      <c r="H26">
+        <v>290</v>
+      </c>
+      <c r="I26">
+        <v>255</v>
+      </c>
+      <c r="J26">
         <v>25</v>
       </c>
-      <c r="H26">
+      <c r="K26">
         <v>5</v>
       </c>
-      <c r="I26" t="str">
-        <v>SKU-0025</v>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="str">
+        <v>PHR-0023</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>مناديل مبللة جونسون للأطفال بدون كحول 72 منديل</v>
+        <v>حفاضات بامبرز مقاس 4 عبوة جامبو 64 حفاضة</v>
       </c>
       <c r="B27" t="str">
-        <v>6221100030044</v>
+        <v>6221100030020</v>
       </c>
       <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
         <v>عناية بالأم والطفل</v>
       </c>
-      <c r="D27" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E27">
-        <v>45</v>
-      </c>
-      <c r="F27">
-        <v>35</v>
-      </c>
-      <c r="G27">
-        <v>40</v>
+      <c r="E27" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>مقاس 4</v>
       </c>
       <c r="H27">
-        <v>8</v>
-      </c>
-      <c r="I27" t="str">
-        <v>SKU-0026</v>
+        <v>320</v>
+      </c>
+      <c r="I27">
+        <v>280</v>
+      </c>
+      <c r="J27">
+        <v>25</v>
+      </c>
+      <c r="K27">
+        <v>5</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="str">
+        <v>PHR-0024</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>شامبو جونسون للأطفال لا دموع بعد اليوم 300 مل</v>
+        <v>حفاضات مولفيكس مقاس 3 عبوة 58 حفاضة</v>
       </c>
       <c r="B28" t="str">
-        <v>6221100030051</v>
+        <v>6221100030037</v>
       </c>
       <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
         <v>عناية بالأم والطفل</v>
       </c>
-      <c r="D28" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E28">
-        <v>65</v>
-      </c>
-      <c r="F28">
-        <v>52</v>
-      </c>
-      <c r="G28">
-        <v>30</v>
+      <c r="E28" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>مقاس 3</v>
       </c>
       <c r="H28">
-        <v>6</v>
-      </c>
-      <c r="I28" t="str">
-        <v>SKU-0027</v>
+        <v>260</v>
+      </c>
+      <c r="I28">
+        <v>228</v>
+      </c>
+      <c r="J28">
+        <v>25</v>
+      </c>
+      <c r="K28">
+        <v>5</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="str">
+        <v>PHR-0025</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>زيت جونسون للأطفال مرطب ناعم 200 مل</v>
+        <v>مناديل مبللة جونسون للأطفال بدون كحول 72 منديل</v>
       </c>
       <c r="B29" t="str">
-        <v>6221100030068</v>
+        <v>6221100030044</v>
       </c>
       <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
         <v>عناية بالأم والطفل</v>
       </c>
-      <c r="D29" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E29">
-        <v>60</v>
-      </c>
-      <c r="F29">
-        <v>48</v>
-      </c>
-      <c r="G29">
-        <v>30</v>
+      <c r="E29" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
       </c>
       <c r="H29">
-        <v>6</v>
-      </c>
-      <c r="I29" t="str">
-        <v>SKU-0028</v>
+        <v>45</v>
+      </c>
+      <c r="I29">
+        <v>35</v>
+      </c>
+      <c r="J29">
+        <v>40</v>
+      </c>
+      <c r="K29">
+        <v>8</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="str">
+        <v>PHR-0026</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>بودرة تلك جونسون للأطفال نقية 200 جم</v>
+        <v>شامبو جونسون للأطفال لا دموع بعد اليوم 300 مل</v>
       </c>
       <c r="B30" t="str">
-        <v>6221100030075</v>
+        <v>6221100030051</v>
       </c>
       <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
         <v>عناية بالأم والطفل</v>
       </c>
-      <c r="D30" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E30">
-        <v>50</v>
-      </c>
-      <c r="F30">
-        <v>39</v>
-      </c>
-      <c r="G30">
-        <v>35</v>
+      <c r="E30" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>300 مل</v>
       </c>
       <c r="H30">
-        <v>7</v>
-      </c>
-      <c r="I30" t="str">
-        <v>SKU-0029</v>
+        <v>65</v>
+      </c>
+      <c r="I30">
+        <v>52</v>
+      </c>
+      <c r="J30">
+        <v>30</v>
+      </c>
+      <c r="K30">
+        <v>6</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="str">
+        <v>PHR-0027</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>كريم سودوكريم لعلاج تسلخات الحفاضات 125 جم</v>
+        <v>زيت جونسون للأطفال مرطب ناعم 200 مل</v>
       </c>
       <c r="B31" t="str">
-        <v>6221100030082</v>
+        <v>6221100030068</v>
       </c>
       <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
         <v>عناية بالأم والطفل</v>
       </c>
-      <c r="D31" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E31">
-        <v>185</v>
-      </c>
-      <c r="F31">
-        <v>152</v>
-      </c>
-      <c r="G31">
-        <v>20</v>
+      <c r="E31" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>200 مل</v>
       </c>
       <c r="H31">
-        <v>4</v>
-      </c>
-      <c r="I31" t="str">
-        <v>SKU-0030</v>
+        <v>60</v>
+      </c>
+      <c r="I31">
+        <v>48</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+      <c r="K31">
+        <v>6</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="str">
+        <v>PHR-0028</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ببرونة أطفال شيكو زجاجية حلمة سيليكون 150 مل</v>
+        <v>بودرة تلك جونسون للأطفال نقية 200 جم</v>
       </c>
       <c r="B32" t="str">
-        <v>6221100030099</v>
+        <v>6221100030075</v>
       </c>
       <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
         <v>عناية بالأم والطفل</v>
       </c>
-      <c r="D32" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E32">
-        <v>95</v>
-      </c>
-      <c r="F32">
-        <v>72</v>
-      </c>
-      <c r="G32">
-        <v>20</v>
+      <c r="E32" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>200 جم</v>
       </c>
       <c r="H32">
-        <v>4</v>
-      </c>
-      <c r="I32" t="str">
-        <v>SKU-0031</v>
+        <v>50</v>
+      </c>
+      <c r="I32">
+        <v>39</v>
+      </c>
+      <c r="J32">
+        <v>35</v>
+      </c>
+      <c r="K32">
+        <v>7</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="str">
+        <v>PHR-0029</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>غسول وجه غارنييه سكين أكتيف فيتامين سي 100 مل</v>
+        <v>كريم سودوكريم لعلاج تسلخات الحفاضات 125 جم</v>
       </c>
       <c r="B33" t="str">
-        <v>6221100040012</v>
+        <v>6221100030082</v>
       </c>
       <c r="C33" t="str">
-        <v>تجميل وعناية بالبشرة</v>
+        <v/>
       </c>
       <c r="D33" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E33">
-        <v>85</v>
-      </c>
-      <c r="F33">
-        <v>68</v>
-      </c>
-      <c r="G33">
-        <v>30</v>
+        <v>عناية بالأم والطفل</v>
+      </c>
+      <c r="E33" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>125 جم</v>
       </c>
       <c r="H33">
-        <v>6</v>
-      </c>
-      <c r="I33" t="str">
-        <v>SKU-0032</v>
+        <v>185</v>
+      </c>
+      <c r="I33">
+        <v>152</v>
+      </c>
+      <c r="J33">
+        <v>20</v>
+      </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="str">
+        <v>PHR-0030</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ماء ميسيلار منظف ومزيل مكياج غارنييه 400 مل</v>
+        <v>ببرونة أطفال شيكو زجاجية حلمة سيليكون 150 مل</v>
       </c>
       <c r="B34" t="str">
-        <v>6221100040029</v>
+        <v>6221100030099</v>
       </c>
       <c r="C34" t="str">
-        <v>تجميل وعناية بالبشرة</v>
+        <v/>
       </c>
       <c r="D34" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E34">
-        <v>110</v>
-      </c>
-      <c r="F34">
-        <v>89</v>
-      </c>
-      <c r="G34">
-        <v>25</v>
+        <v>عناية بالأم والطفل</v>
+      </c>
+      <c r="E34" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>150 مل</v>
       </c>
       <c r="H34">
-        <v>5</v>
-      </c>
-      <c r="I34" t="str">
-        <v>SKU-0033</v>
+        <v>95</v>
+      </c>
+      <c r="I34">
+        <v>72</v>
+      </c>
+      <c r="J34">
+        <v>20</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="str">
+        <v>PHR-0031</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>كريم نيفيا سوفت مرطب منعش للجسم والوجه 200 مل</v>
+        <v>غسول وجه غارنييه سكين أكتيف فيتامين سي 100 مل</v>
       </c>
       <c r="B35" t="str">
-        <v>6221100040036</v>
+        <v>6221100040012</v>
       </c>
       <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D35" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E35">
-        <v>75</v>
-      </c>
-      <c r="F35">
-        <v>58</v>
-      </c>
-      <c r="G35">
-        <v>35</v>
+      <c r="E35" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>100 مل</v>
       </c>
       <c r="H35">
-        <v>7</v>
-      </c>
-      <c r="I35" t="str">
-        <v>SKU-0034</v>
+        <v>85</v>
+      </c>
+      <c r="I35">
+        <v>68</v>
+      </c>
+      <c r="J35">
+        <v>30</v>
+      </c>
+      <c r="K35">
+        <v>6</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="str">
+        <v>PHR-0032</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>كريم نيفيا أزرق كلاسيك علبة معدنية 150 مل</v>
+        <v>ماء ميسيلار منظف ومزيل مكياج غارنييه 400 مل</v>
       </c>
       <c r="B36" t="str">
-        <v>6221100040043</v>
+        <v>6221100040029</v>
       </c>
       <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D36" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E36">
-        <v>65</v>
-      </c>
-      <c r="F36">
-        <v>51</v>
-      </c>
-      <c r="G36">
-        <v>40</v>
+      <c r="E36" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>400 مل</v>
       </c>
       <c r="H36">
-        <v>8</v>
-      </c>
-      <c r="I36" t="str">
-        <v>SKU-0035</v>
+        <v>110</v>
+      </c>
+      <c r="I36">
+        <v>89</v>
+      </c>
+      <c r="J36">
+        <v>25</v>
+      </c>
+      <c r="K36">
+        <v>5</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="str">
+        <v>PHR-0033</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>صن بلوك واقي شمس بوباي جل SPF50+ 50 جم</v>
+        <v>كريم نيفيا سوفت مرطب منعش للجسم والوجه 200 مل</v>
       </c>
       <c r="B37" t="str">
-        <v>6221100040050</v>
+        <v>6221100040036</v>
       </c>
       <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D37" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E37">
-        <v>160</v>
-      </c>
-      <c r="F37">
-        <v>128</v>
-      </c>
-      <c r="G37">
-        <v>20</v>
+      <c r="E37" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>200 مل</v>
       </c>
       <c r="H37">
-        <v>4</v>
-      </c>
-      <c r="I37" t="str">
-        <v>SKU-0036</v>
+        <v>75</v>
+      </c>
+      <c r="I37">
+        <v>58</v>
+      </c>
+      <c r="J37">
+        <v>35</v>
+      </c>
+      <c r="K37">
+        <v>7</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="str">
+        <v>PHR-0034</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>سيروم شعر سيروبايب كيراتين مضاد للتساقط 100 مل</v>
+        <v>كريم نيفيا أزرق كلاسيك علبة معدنية 150 مل</v>
       </c>
       <c r="B38" t="str">
-        <v>6221100040067</v>
+        <v>6221100040043</v>
       </c>
       <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D38" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E38">
-        <v>195</v>
-      </c>
-      <c r="F38">
-        <v>155</v>
-      </c>
-      <c r="G38">
-        <v>15</v>
+      <c r="E38" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>150 مل</v>
       </c>
       <c r="H38">
-        <v>3</v>
-      </c>
-      <c r="I38" t="str">
-        <v>SKU-0037</v>
+        <v>65</v>
+      </c>
+      <c r="I38">
+        <v>51</v>
+      </c>
+      <c r="J38">
+        <v>40</v>
+      </c>
+      <c r="K38">
+        <v>8</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="str">
+        <v>PHR-0035</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>حمام كريم شعر فاتيكا بالثوم والنخاع 500 جم</v>
+        <v>صن بلوك واقي شمس بوباي جل SPF50+ 50 جم</v>
       </c>
       <c r="B39" t="str">
-        <v>6221100040074</v>
+        <v>6221100040050</v>
       </c>
       <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D39" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E39">
-        <v>65</v>
-      </c>
-      <c r="F39">
-        <v>50</v>
-      </c>
-      <c r="G39">
-        <v>30</v>
+      <c r="E39" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>50 جم</v>
       </c>
       <c r="H39">
-        <v>6</v>
-      </c>
-      <c r="I39" t="str">
-        <v>SKU-0038</v>
+        <v>160</v>
+      </c>
+      <c r="I39">
+        <v>128</v>
+      </c>
+      <c r="J39">
+        <v>20</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="str">
+        <v>PHR-0036</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>مزيل عرق ريكسونا بخاخ رجالي 150 مل حماية 48 ساعة</v>
+        <v>سيروم شعر سيروبايب كيراتين مضاد للتساقط 100 مل</v>
       </c>
       <c r="B40" t="str">
-        <v>6221100040081</v>
+        <v>6221100040067</v>
       </c>
       <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D40" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E40">
-        <v>75</v>
-      </c>
-      <c r="F40">
-        <v>59</v>
-      </c>
-      <c r="G40">
-        <v>35</v>
+      <c r="E40" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>100 مل</v>
       </c>
       <c r="H40">
-        <v>7</v>
-      </c>
-      <c r="I40" t="str">
-        <v>SKU-0039</v>
+        <v>195</v>
+      </c>
+      <c r="I40">
+        <v>155</v>
+      </c>
+      <c r="J40">
+        <v>15</v>
+      </c>
+      <c r="K40">
+        <v>3</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="str">
+        <v>PHR-0037</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>مزيل عرق نيفيا رول أون حريمي 50 مل حماية جافة</v>
+        <v>حمام كريم شعر فاتيكا بالثوم والنخاع 500 جم</v>
       </c>
       <c r="B41" t="str">
-        <v>6221100040098</v>
+        <v>6221100040074</v>
       </c>
       <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D41" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E41">
-        <v>55</v>
-      </c>
-      <c r="F41">
-        <v>42</v>
-      </c>
-      <c r="G41">
-        <v>40</v>
+      <c r="E41" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>500 جم</v>
       </c>
       <c r="H41">
-        <v>8</v>
-      </c>
-      <c r="I41" t="str">
-        <v>SKU-0040</v>
+        <v>65</v>
+      </c>
+      <c r="I41">
+        <v>50</v>
+      </c>
+      <c r="J41">
+        <v>30</v>
+      </c>
+      <c r="K41">
+        <v>6</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="str">
+        <v>PHR-0038</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>معجون أسنان سنسوداين للأسنان الحساسة 75 مل</v>
+        <v>مزيل عرق ريكسونا بخاخ رجالي 150 مل حماية 48 ساعة</v>
       </c>
       <c r="B42" t="str">
-        <v>6221100040104</v>
+        <v>6221100040081</v>
       </c>
       <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D42" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E42">
-        <v>65</v>
-      </c>
-      <c r="F42">
-        <v>52</v>
-      </c>
-      <c r="G42">
+      <c r="E42" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>150 مل</v>
+      </c>
+      <c r="H42">
+        <v>75</v>
+      </c>
+      <c r="I42">
+        <v>59</v>
+      </c>
+      <c r="J42">
         <v>35</v>
       </c>
-      <c r="H42">
+      <c r="K42">
         <v>7</v>
       </c>
-      <c r="I42" t="str">
-        <v>SKU-0041</v>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="str">
+        <v>PHR-0039</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
+        <v>مزيل عرق نيفيا رول أون حريمي 50 مل حماية جافة</v>
+      </c>
+      <c r="B43" t="str">
+        <v>6221100040098</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v>تجميل وعناية بالبشرة</v>
+      </c>
+      <c r="E43" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>50 مل</v>
+      </c>
+      <c r="H43">
+        <v>55</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>40</v>
+      </c>
+      <c r="K43">
+        <v>8</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="str">
+        <v>PHR-0040</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>معجون أسنان سنسوداين للأسنان الحساسة 75 مل</v>
+      </c>
+      <c r="B44" t="str">
+        <v>6221100040104</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v>تجميل وعناية بالبشرة</v>
+      </c>
+      <c r="E44" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>75 مل</v>
+      </c>
+      <c r="H44">
+        <v>65</v>
+      </c>
+      <c r="I44">
+        <v>52</v>
+      </c>
+      <c r="J44">
+        <v>35</v>
+      </c>
+      <c r="K44">
+        <v>7</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="str">
+        <v>PHR-0041</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v>موس حلاقة جيليت بلو 3 شفرات متحركة كيس 4 قطع</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B45" t="str">
         <v>6221100040111</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
         <v>تجميل وعناية بالبشرة</v>
       </c>
-      <c r="D43" t="str">
-        <v>قطعة</v>
-      </c>
-      <c r="E43">
+      <c r="E45" t="str">
+        <v>قطعة</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45">
         <v>55</v>
       </c>
-      <c r="F43">
+      <c r="I45">
         <v>42</v>
       </c>
-      <c r="G43">
+      <c r="J45">
         <v>40</v>
       </c>
-      <c r="H43">
+      <c r="K45">
         <v>8</v>
       </c>
-      <c r="I43" t="str">
-        <v>SKU-0042</v>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="str">
+        <v>PHR-0042</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
   </ignoredErrors>
 </worksheet>
 </file>